--- a/output/ATI_buyout_client_serviceable.xlsx
+++ b/output/ATI_buyout_client_serviceable.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Лист2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист2'!$A$1:$G$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист2'!$A$1:$G$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -808,44 +808,44 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AS3510-0218C</t>
+          <t>979998-3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CABLE</t>
+          <t>VALVE, BLEED, SHUTOFF, ISOLATION</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>OH, R</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>249</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>979998-3</t>
+          <t>979998-1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VALVE, BLEED, SHUTOFF, ISOLATION</t>
+          <t>VALVE, SHUTOFF, PRESSURE REGULATING</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>OH, R</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
@@ -870,18 +870,18 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>979998-1</t>
+          <t>AE0607F00</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VALVE, SHUTOFF, PRESSURE REGULATING</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
@@ -901,18 +901,18 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AE0607F00</t>
+          <t>822-1115-001</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>TRANSCEIVER-VHF</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -922,28 +922,28 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>OH, R</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>822-1115-001</t>
+          <t>GM9584-1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>TRANSCEIVER-VHF</t>
+          <t>POSN FEEDBACK SENSOR (RVDT)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -953,28 +953,28 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>OH, R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GM9584-1</t>
+          <t>1659-1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>POSN FEEDBACK SENSOR (RVDT)</t>
+          <t>EMERGENCY BATTERY</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -984,59 +984,59 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R, SV</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>600-10910-5</t>
+          <t>622-9818-020</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>COMPUTER, IAPS MAINTENANCE</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1659-1</t>
+          <t>822-0044-001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EMERGENCY BATTERY</t>
+          <t>FMC-4100 FLIGHT MANAGEMENT COMPUTER</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>R, SV</t>
+          <t>IT, OH</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
@@ -1056,18 +1056,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>622-9818-020</t>
+          <t>601R93030-1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COMPUTER, IAPS MAINTENANCE</t>
+          <t>SHIM</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
@@ -1087,18 +1087,18 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>822-0044-001</t>
+          <t>601R93030-3</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>FMC-4100 FLIGHT MANAGEMENT COMPUTER</t>
+          <t>TRANSMITTER ASSY, FLAP POSITION</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1108,90 +1108,90 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>IT, OH</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>47407-2WE</t>
+          <t>27000-7</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>BRUSH ASSY</t>
+          <t>SPOILERON POWER CONTROL UNIT</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AR10105-213A1H</t>
+          <t>35563-2-310</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SEAL, TEFLON</t>
+          <t>ELEMENT</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>601R93030-1</t>
+          <t>MXP411-3</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SHIM</t>
+          <t>BOX, STOWAGE</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
@@ -1211,23 +1211,23 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>601R93030-3</t>
+          <t>38E93-6</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>TRANSMITTER ASSY, FLAP POSITION</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1242,18 +1242,18 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>27000-7</t>
+          <t>473597-19</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SPOILERON POWER CONTROL UNIT</t>
+          <t>SMOKE DETECTOR</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
@@ -1273,23 +1273,23 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>35563-2-310</t>
+          <t>170080-00</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ELEMENT</t>
+          <t>VALVE</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1304,18 +1304,18 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MXP411-3</t>
+          <t>G601R783202-1</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>BOX, STOWAGE</t>
+          <t>TOOL KIT-THRUST REVERSER</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20-00</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
@@ -1335,28 +1335,28 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>38E93-6</t>
+          <t>140-153</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>ANTI SKID TRANSDUCER</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
@@ -1366,28 +1366,28 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>473597-19</t>
+          <t>10C10F</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SMOKE DETECTOR</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
@@ -1397,18 +1397,18 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>170080-00</t>
+          <t>853D100-24</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VALVE</t>
+          <t>RIGHT WING OUTBOARD FLAP ACTUATOR</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1418,28 +1418,28 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>G601R783202-1</t>
+          <t>854D100-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TOOL KIT-THRUST REVERSER</t>
+          <t>ACTUATOR - OUTBD</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>20-00</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1449,28 +1449,28 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>OH, R, SV</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>140-153</t>
+          <t>854D100-24</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>ANTI SKID TRANSDUCER</t>
+          <t>RIGHT WING OUTBOARD FLAP ACTUATOR</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1480,28 +1480,28 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R, SV, T</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>13600LA902A3</t>
+          <t>808440-2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIBRATION DAMPER</t>
+          <t>VALVE ASSY, DUAL BYPASS</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1511,33 +1511,33 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OH, SV</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>7600763</t>
+          <t>517212-4</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>IDG FILTER</t>
+          <t>IGNITER</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>737MAX</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1546,91 +1546,91 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AS1895-23-200</t>
+          <t>QAR200-03-00</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>RECORDER</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>737MAX</t>
+          <t>BOEING</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>IT, SV</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>601R97210-1</t>
+          <t>472597-02</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>DETECTOR ASSY</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>I, M, SV</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>160-10741-260</t>
+          <t>2534M54P02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VISOR-SUN,WINDSHIELD</t>
+          <t>GASKET-SEAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>737MAX</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1639,24 +1639,24 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>10C10F</t>
+          <t>ZCD-B9A-023</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>CONTACTOR, GENERATOR</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1666,28 +1666,28 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>SV, T</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AS3582-246</t>
+          <t>8ES005421-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>MULTI. CONTROL &amp; DISPLAY UNIT</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1697,28 +1697,28 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R, SV</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>KFN587-08</t>
+          <t>979626-3-1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>KAYNAR NUT</t>
+          <t>VALVE, ISOLATION SHUTOFF</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1728,23 +1728,23 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OH, R</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>P2-07-0021-002</t>
+          <t>168000VI-44</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>BATTERY</t>
+          <t>SCREW</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>737MAX</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>7</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>770440</t>
+          <t>AE1410CA1</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>HOUSING</t>
+          <t>FAN- AVIONIC EXHAUST</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
@@ -1800,85 +1800,85 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>9534663</t>
+          <t>27600-3</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>PLUG</t>
+          <t>VALVE ASSY</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>M83248-1-034</t>
+          <t>622-9821-002</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>DATA PROCESSING UNIT</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>E0399-01</t>
+          <t>MS17826-20</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>DISCHARGER-STATIC</t>
+          <t>NUT, SELF-LKG, CASTELLATED, REDUCED</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -1887,29 +1887,29 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>0727540</t>
+          <t>49-337</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SHROUD</t>
+          <t>CABIN PRESSURE INDICATOR</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -1918,29 +1918,29 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AS1895-23-300</t>
+          <t>AE87771G</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>SEAL-RING</t>
+          <t>FITTING</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>737MAX</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -1949,34 +1949,34 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>5010546</t>
+          <t>E03A00</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>TUBE SUBASSEMBLY</t>
+          <t>VALVE ASSY-FIRE SHUTOFF</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
@@ -1986,13 +1986,13 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>20-630</t>
+          <t>C20105000-2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>TACHOMETER</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2007,33 +2007,33 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>N40-1B10100-101</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>CYLINDER, TRANSFER</t>
+          <t>HANDSET ASSY-COCKPIT</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2048,18 +2048,18 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>009519-09</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>LAMP, HALOGEN</t>
+          <t>CRT DETECTOR, LOW FLOW</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2073,19 +2073,19 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>CEC-08</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CAP</t>
+          <t>RHEOSTAT</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>B735</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2104,24 +2104,24 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>53-288</t>
+          <t>4913211080</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CLIP</t>
+          <t>PAD</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2131,85 +2131,85 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>CVC4232-16</t>
+          <t>8-405-06</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>PROXIMITY SWITCH</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>565-101</t>
+          <t>MS25083-5BB4</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>LAMP</t>
+          <t>ROPE GROUND</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>M83461-1-219</t>
+          <t>6100945</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>BULB</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2228,29 +2228,29 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ABS0604-4</t>
+          <t>AS3209-136</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>WASHER</t>
+          <t>O-RING</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -2259,19 +2259,19 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>69494K113WE</t>
+          <t>MS24694C56</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>SCREW</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2286,33 +2286,33 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>504-175</t>
+          <t>30H673</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>BRACKET AND RELAY INSTL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2324,1682 +2324,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>2-162N602-70</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr"/>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>INFANT LIFE VEST</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>A321</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>ABS0338-01</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr"/>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>WASHER-LOCK</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>A321</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>853D100-24</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr"/>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>RIGHT WING OUTBOARD FLAP ACTUATOR</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>854D100-23</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>ACTUATOR - OUTBD</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>OH, R, SV</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>854D100-24</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr"/>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>RIGHT WING OUTBOARD FLAP ACTUATOR</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>R, SV, T</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>808440-2</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr"/>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>VALVE ASSY, DUAL BYPASS</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>OH, SV</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>517212-4</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr"/>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>IGNITER</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>737MAX</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>9DR408176-01</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>STROBE, XENON</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>N, SV</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>QAR200-03-00</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr"/>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>RECORDER</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>BOEING</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>IT, SV</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>472597-02</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr"/>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>DETECTOR ASSY</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>I, M, SV</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>2534M54P02</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr"/>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>GASKET-SEAL</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>737MAX</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>ZCD-B9A-023</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>CONTACTOR, GENERATOR</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>SV, T</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>8ES005421-09</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr"/>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>MULTI. CONTROL &amp; DISPLAY UNIT</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>R, SV</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>979626-3-1</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>VALVE, ISOLATION SHUTOFF</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>OH, R</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>168000VI-44</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr"/>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>SCREW</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>AE1410CA1</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>FAN- AVIONIC EXHAUST</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>27600-3</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr"/>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>VALVE ASSY</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>622-9821-002</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>DATA PROCESSING UNIT</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>MS17826-20</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr"/>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>NUT, SELF-LKG, CASTELLATED, REDUCED</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>49-337</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>CABIN PRESSURE INDICATOR</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>AE87771G</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr"/>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>FITTING</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>BR9805-007</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr"/>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>LAMP</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>B734</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>M81714/12-16D-2</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr"/>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>DBL SPLICE</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>E03A00</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr"/>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>VALVE ASSY-FIRE SHUTOFF</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>A321</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>C20105000-2</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr"/>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>TACHOMETER</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>A321</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>68-1156</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr"/>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>PACKING</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>N40-1B10100-101</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr"/>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>HANDSET ASSY-COCKPIT</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>A321</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>009519-09</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr"/>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>CRT DETECTOR, LOW FLOW</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>26405</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr"/>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>RHEOSTAT</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>B735</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>2-12SC1</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>DISCHARGER</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>4913211080</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr"/>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>PAD</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>A321</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>8-405-06</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr"/>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>PROXIMITY SWITCH</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>WL305</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr"/>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>LAMP</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>737ALL</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>4002-SW-SS</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr"/>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>GROMMET</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>N, S</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>AS1895-23-150</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr"/>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>SEAL</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>737MAX</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>P52-7893</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr"/>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>FILTER ASSY, AIR</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>DAN152-1</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr"/>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>TDP-TIEDOWN POINT</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>A321</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>WF336733</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr"/>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>FILTER</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>MS25083-5BB4</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr"/>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>ROPE GROUND</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>AS1895-23-250</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr"/>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>SEAL-RING</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>737MAX</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>AS1895-23-175</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr"/>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>SEAL-RING</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>737MAX</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>68-1364</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr"/>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>PACKING, PREFORMED</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>A321</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>7700525</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr"/>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>GRID</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>APN3111062-13</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr"/>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>RING</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>6100945</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr"/>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>BULB</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>MS21250-04012</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr"/>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>BOLT, 12 POINT HD</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>MS16562-39</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr"/>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>PIN, ROLL</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>J1438P009</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr"/>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>PACKING-PREFORMED</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>737MAX</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>21AJ069-1</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr"/>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>DRAIN</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>A321</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>2534M51P02</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr"/>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>GASKET-SEAL FLANGE</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>737MAX</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>AS3209-136</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr"/>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>O-RING</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>MS24694C56</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr"/>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>SCREW</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>MS20230GBP2</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr"/>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>GROMMET</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>30H673</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr"/>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>BRACKET AND RELAY INSTL</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G114"/>
+  <autoFilter ref="A1:G60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>